--- a/informes_data/Segunda FEB/2025-26/playoffs/aggregate/AGGREGATE_CLASS BASQUET SANT ANTONI.xlsx
+++ b/informes_data/Segunda FEB/2025-26/playoffs/aggregate/AGGREGATE_CLASS BASQUET SANT ANTONI.xlsx
@@ -647,127 +647,127 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>364.2</v>
+        <v>440.48</v>
       </c>
       <c r="C2" t="n">
-        <v>359.8799999999999</v>
+        <v>435.1399999999999</v>
       </c>
       <c r="D2" t="n">
-        <v>117.2613093253307</v>
+        <v>113.2968699728823</v>
       </c>
       <c r="E2" t="n">
-        <v>99.75547404690454</v>
+        <v>95.37160454106726</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5286532951289399</v>
+        <v>0.5167865707434053</v>
       </c>
       <c r="G2" t="n">
-        <v>0.1192113709307657</v>
+        <v>0.1343475628216773</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3673469387755102</v>
+        <v>0.3697478991596639</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1518624641833811</v>
+        <v>0.1486810551558753</v>
       </c>
       <c r="J2" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="K2" t="n">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="L2" t="n">
-        <v>44</v>
+        <v>65</v>
       </c>
       <c r="M2" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="N2" t="n">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="O2" t="n">
-        <v>104</v>
+        <v>128</v>
       </c>
       <c r="P2" t="n">
-        <v>0.2979942693409742</v>
+        <v>0.3069544364508393</v>
       </c>
       <c r="Q2" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="R2" t="n">
-        <v>64</v>
+        <v>78</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1833810888252149</v>
+        <v>0.1870503597122302</v>
       </c>
       <c r="T2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="U2" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="V2" t="n">
-        <v>0.09742120343839542</v>
+        <v>0.08872901678657075</v>
       </c>
       <c r="W2" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="X2" t="n">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.1260744985673352</v>
+        <v>0.1223021582733813</v>
       </c>
       <c r="Z2" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="AA2" t="n">
-        <v>103</v>
+        <v>123</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.2951289398280803</v>
+        <v>0.2949640287769784</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.53125</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.46875</v>
+        <v>0.4743589743589743</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.3529411764705883</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.25</v>
+        <v>0.2549019607843137</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.4660194174757282</v>
+        <v>0.4227642276422764</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.038461538461539</v>
+        <v>1.0625</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.7058823529411765</v>
+        <v>0.7027027027027027</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.204081632653061</v>
+        <v>1.120689655172414</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.5666666666666667</v>
+        <v>0.5316455696202531</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.5972222222222222</v>
+        <v>0.6022727272727273</v>
       </c>
       <c r="AM2" t="n">
-        <v>2.2</v>
+        <v>2.241379310344827</v>
       </c>
       <c r="AN2" t="n">
-        <v>1.519230769230769</v>
+        <v>1.338028169014085</v>
       </c>
       <c r="AO2" t="n">
-        <v>6.711538461538462</v>
+        <v>5.873239436619718</v>
       </c>
       <c r="AP2" t="n">
-        <v>8.23076923076923</v>
+        <v>7.211267605633803</v>
       </c>
     </row>
     <row r="3">
@@ -777,127 +777,127 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>72.84</v>
+        <v>73.41333333333334</v>
       </c>
       <c r="C3" t="n">
-        <v>71.97599999999998</v>
+        <v>72.52333333333333</v>
       </c>
       <c r="D3" t="n">
-        <v>117.2613093253307</v>
+        <v>113.2968699728823</v>
       </c>
       <c r="E3" t="n">
-        <v>99.75547404690454</v>
+        <v>95.37160454106726</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5286532951289399</v>
+        <v>0.5167865707434054</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1192113709307657</v>
+        <v>0.1343475628216773</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3673469387755102</v>
+        <v>0.3697478991596639</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1518624641833811</v>
+        <v>0.1486810551558753</v>
       </c>
       <c r="J3" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="K3" t="n">
-        <v>8.6</v>
+        <v>8.833333333333334</v>
       </c>
       <c r="L3" t="n">
-        <v>8.800000000000001</v>
+        <v>10.83333333333333</v>
       </c>
       <c r="M3" t="n">
-        <v>3.2</v>
+        <v>4.5</v>
       </c>
       <c r="N3" t="n">
-        <v>10.8</v>
+        <v>11.33333333333333</v>
       </c>
       <c r="O3" t="n">
-        <v>20.8</v>
+        <v>21.33333333333333</v>
       </c>
       <c r="P3" t="n">
-        <v>0.2979942693409742</v>
+        <v>0.3069544364508393</v>
       </c>
       <c r="Q3" t="n">
-        <v>6</v>
+        <v>6.166666666666667</v>
       </c>
       <c r="R3" t="n">
-        <v>12.8</v>
+        <v>13</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1833810888252149</v>
+        <v>0.1870503597122302</v>
       </c>
       <c r="T3" t="n">
-        <v>2.4</v>
+        <v>2.166666666666667</v>
       </c>
       <c r="U3" t="n">
-        <v>6.8</v>
+        <v>6.166666666666667</v>
       </c>
       <c r="V3" t="n">
-        <v>0.09742120343839542</v>
+        <v>0.08872901678657075</v>
       </c>
       <c r="W3" t="n">
-        <v>2.2</v>
+        <v>2.166666666666667</v>
       </c>
       <c r="X3" t="n">
-        <v>8.800000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.1260744985673353</v>
+        <v>0.1223021582733813</v>
       </c>
       <c r="Z3" t="n">
-        <v>9.6</v>
+        <v>8.666666666666666</v>
       </c>
       <c r="AA3" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.2951289398280803</v>
+        <v>0.2949640287769784</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.5192307692307693</v>
+        <v>0.5312500000000001</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.46875</v>
+        <v>0.4743589743589744</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.3529411764705883</v>
+        <v>0.3513513513513513</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.25</v>
+        <v>0.2549019607843137</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.4660194174757281</v>
+        <v>0.4227642276422764</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.038461538461539</v>
+        <v>1.0625</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.7058823529411765</v>
+        <v>0.7027027027027026</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.204081632653061</v>
+        <v>1.120689655172414</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.5666666666666667</v>
+        <v>0.5316455696202532</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.5972222222222222</v>
+        <v>0.6022727272727273</v>
       </c>
       <c r="AM3" t="n">
-        <v>2.2</v>
+        <v>2.241379310344828</v>
       </c>
       <c r="AN3" t="n">
-        <v>1.519230769230769</v>
+        <v>1.338028169014085</v>
       </c>
       <c r="AO3" t="n">
-        <v>6.711538461538461</v>
+        <v>5.873239436619718</v>
       </c>
       <c r="AP3" t="n">
-        <v>8.23076923076923</v>
+        <v>7.211267605633802</v>
       </c>
     </row>
     <row r="4">
@@ -907,127 +907,127 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>355.56</v>
+        <v>429.8</v>
       </c>
       <c r="C4" t="n">
-        <v>359.8799999999999</v>
+        <v>435.1399999999999</v>
       </c>
       <c r="D4" t="n">
-        <v>99.75547404690454</v>
+        <v>95.37160454106726</v>
       </c>
       <c r="E4" t="n">
-        <v>117.2613093253307</v>
+        <v>113.2968699728823</v>
       </c>
       <c r="F4" t="n">
-        <v>0.4487179487179487</v>
+        <v>0.4412568306010929</v>
       </c>
       <c r="G4" t="n">
-        <v>0.1443834825295986</v>
+        <v>0.1586982723985536</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2985074626865671</v>
+        <v>0.2893617021276595</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2532051282051282</v>
+        <v>0.2513661202185792</v>
       </c>
       <c r="J4" t="n">
+        <v>45</v>
+      </c>
+      <c r="K4" t="n">
         <v>40</v>
       </c>
-      <c r="K4" t="n">
+      <c r="L4" t="n">
+        <v>74</v>
+      </c>
+      <c r="M4" t="n">
+        <v>39</v>
+      </c>
+      <c r="N4" t="n">
+        <v>64</v>
+      </c>
+      <c r="O4" t="n">
+        <v>107</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.2923497267759563</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>20</v>
+      </c>
+      <c r="R4" t="n">
+        <v>71</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.1939890710382514</v>
+      </c>
+      <c r="T4" t="n">
+        <v>13</v>
+      </c>
+      <c r="U4" t="n">
         <v>37</v>
       </c>
-      <c r="L4" t="n">
-        <v>62</v>
-      </c>
-      <c r="M4" t="n">
-        <v>31</v>
-      </c>
-      <c r="N4" t="n">
-        <v>55</v>
-      </c>
-      <c r="O4" t="n">
-        <v>94</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0.3012820512820513</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>17</v>
-      </c>
-      <c r="R4" t="n">
-        <v>61</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0.1955128205128205</v>
-      </c>
-      <c r="T4" t="n">
-        <v>11</v>
-      </c>
-      <c r="U4" t="n">
-        <v>30</v>
-      </c>
       <c r="V4" t="n">
-        <v>0.09615384615384616</v>
+        <v>0.1010928961748634</v>
       </c>
       <c r="W4" t="n">
         <v>5</v>
       </c>
       <c r="X4" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.09294871794871795</v>
+        <v>0.08469945355191257</v>
       </c>
       <c r="Z4" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="AA4" t="n">
-        <v>98</v>
+        <v>120</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.3141025641025641</v>
+        <v>0.3278688524590164</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.5851063829787234</v>
+        <v>0.5981308411214953</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.2786885245901639</v>
+        <v>0.2816901408450704</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.3666666666666666</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.1724137931034483</v>
+        <v>0.1612903225806452</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.336734693877551</v>
+        <v>0.3166666666666667</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.170212765957447</v>
+        <v>1.196261682242991</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.7333333333333333</v>
+        <v>0.7027027027027027</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.8976377952755905</v>
+        <v>0.8543046357615894</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.7692307692307693</v>
+        <v>0.6338028169014085</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.6166666666666667</v>
+        <v>0.5882352941176471</v>
       </c>
       <c r="AM4" t="n">
-        <v>1.878787878787879</v>
+        <v>1.947368421052632</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.9833333333333333</v>
+        <v>0.8481012658227848</v>
       </c>
       <c r="AO4" t="n">
-        <v>5.2</v>
+        <v>4.632911392405063</v>
       </c>
       <c r="AP4" t="n">
-        <v>6.183333333333334</v>
+        <v>5.481012658227848</v>
       </c>
     </row>
     <row r="5">
@@ -1037,127 +1037,127 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>71.11199999999999</v>
+        <v>71.63333333333334</v>
       </c>
       <c r="C5" t="n">
-        <v>71.97599999999998</v>
+        <v>72.52333333333333</v>
       </c>
       <c r="D5" t="n">
-        <v>99.75547404690454</v>
+        <v>95.37160454106726</v>
       </c>
       <c r="E5" t="n">
-        <v>117.2613093253307</v>
+        <v>113.2968699728823</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4487179487179487</v>
+        <v>0.4412568306010929</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1443834825295986</v>
+        <v>0.1586982723985536</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2985074626865671</v>
+        <v>0.2893617021276596</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2532051282051282</v>
+        <v>0.2513661202185792</v>
       </c>
       <c r="J5" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="K5" t="n">
-        <v>7.4</v>
+        <v>6.666666666666667</v>
       </c>
       <c r="L5" t="n">
-        <v>12.4</v>
+        <v>12.33333333333333</v>
       </c>
       <c r="M5" t="n">
-        <v>6.2</v>
+        <v>6.5</v>
       </c>
       <c r="N5" t="n">
-        <v>11</v>
+        <v>10.66666666666667</v>
       </c>
       <c r="O5" t="n">
-        <v>18.8</v>
+        <v>17.83333333333333</v>
       </c>
       <c r="P5" t="n">
-        <v>0.3012820512820513</v>
+        <v>0.2923497267759563</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.4</v>
+        <v>3.333333333333333</v>
       </c>
       <c r="R5" t="n">
-        <v>12.2</v>
+        <v>11.83333333333333</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1955128205128205</v>
+        <v>0.1939890710382514</v>
       </c>
       <c r="T5" t="n">
-        <v>2.2</v>
+        <v>2.166666666666667</v>
       </c>
       <c r="U5" t="n">
-        <v>6</v>
+        <v>6.166666666666667</v>
       </c>
       <c r="V5" t="n">
-        <v>0.09615384615384616</v>
+        <v>0.1010928961748634</v>
       </c>
       <c r="W5" t="n">
-        <v>1</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="X5" t="n">
-        <v>5.8</v>
+        <v>5.166666666666667</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.09294871794871795</v>
+        <v>0.08469945355191258</v>
       </c>
       <c r="Z5" t="n">
-        <v>6.6</v>
+        <v>6.333333333333333</v>
       </c>
       <c r="AA5" t="n">
-        <v>19.6</v>
+        <v>20</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.3141025641025642</v>
+        <v>0.3278688524590164</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.5851063829787234</v>
+        <v>0.5981308411214953</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.278688524590164</v>
+        <v>0.2816901408450704</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.3666666666666667</v>
+        <v>0.3513513513513513</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.1724137931034483</v>
+        <v>0.1612903225806452</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.336734693877551</v>
+        <v>0.3166666666666667</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.170212765957447</v>
+        <v>1.196261682242991</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.7333333333333334</v>
+        <v>0.7027027027027026</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.8976377952755904</v>
+        <v>0.8543046357615893</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.7692307692307692</v>
+        <v>0.6338028169014084</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.6166666666666667</v>
+        <v>0.5882352941176471</v>
       </c>
       <c r="AM5" t="n">
-        <v>1.878787878787879</v>
+        <v>1.947368421052632</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.9833333333333334</v>
+        <v>0.8481012658227848</v>
       </c>
       <c r="AO5" t="n">
-        <v>5.2</v>
+        <v>4.632911392405063</v>
       </c>
       <c r="AP5" t="n">
-        <v>6.183333333333334</v>
+        <v>5.481012658227849</v>
       </c>
     </row>
     <row r="7">
@@ -1429,40 +1429,40 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C8" t="n">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="D8" t="n">
         <v>2</v>
       </c>
       <c r="E8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F8" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="G8" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="H8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J8" t="n">
         <v>4</v>
       </c>
       <c r="K8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L8" t="n">
         <v>3</v>
       </c>
       <c r="M8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
@@ -1471,19 +1471,19 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q8" t="n">
         <v>3</v>
       </c>
-      <c r="Q8" t="n">
-        <v>2</v>
-      </c>
       <c r="R8" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="U8" t="n">
         <v>3</v>
@@ -1492,10 +1492,10 @@
         <v>0</v>
       </c>
       <c r="W8" t="n">
+        <v>9</v>
+      </c>
+      <c r="X8" t="n">
         <v>3</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1</v>
       </c>
       <c r="Y8" t="n">
         <v>0</v>
@@ -1519,72 +1519,72 @@
         <v>2</v>
       </c>
       <c r="AF8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AH8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AI8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.417</v>
+        <v>0.462</v>
       </c>
       <c r="AK8" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="AL8" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.55</v>
+        <v>0.556</v>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>114:18</t>
+          <t>147:08</t>
         </is>
       </c>
       <c r="AO8" t="n">
-        <v>39.88</v>
+        <v>51.32</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.722</v>
+        <v>0.744</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.719</v>
+        <v>0.745</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.329</v>
+        <v>1.345</v>
       </c>
       <c r="AS8" t="n">
-        <v>0.075</v>
+        <v>0.097</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.028</v>
+        <v>0.044</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.333</v>
+        <v>0.8</v>
       </c>
       <c r="AV8" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AW8" t="n">
-        <v>13.333</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.16</v>
+        <v>0.158</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.027</v>
+        <v>0.021</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.052</v>
+        <v>0.049</v>
       </c>
       <c r="BA8" t="n">
-        <v>0.029</v>
+        <v>0.025</v>
       </c>
     </row>
     <row r="9">
@@ -1594,61 +1594,61 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C9" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D9" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E9" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="F9" t="n">
         <v>10</v>
       </c>
       <c r="G9" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="H9" t="n">
         <v>2</v>
       </c>
       <c r="I9" t="n">
+        <v>7</v>
+      </c>
+      <c r="J9" t="n">
+        <v>19</v>
+      </c>
+      <c r="K9" t="n">
+        <v>14</v>
+      </c>
+      <c r="L9" t="n">
+        <v>5</v>
+      </c>
+      <c r="M9" t="n">
+        <v>7</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1</v>
+      </c>
+      <c r="P9" t="n">
         <v>6</v>
       </c>
-      <c r="J9" t="n">
-        <v>17</v>
-      </c>
-      <c r="K9" t="n">
-        <v>10</v>
-      </c>
-      <c r="L9" t="n">
-        <v>3</v>
-      </c>
-      <c r="M9" t="n">
-        <v>4</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>5</v>
-      </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R9" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="U9" t="n">
         <v>2</v>
@@ -1657,28 +1657,28 @@
         <v>2</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Z9" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.455</v>
+        <v>0.429</v>
       </c>
       <c r="AB9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AC9" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.6</v>
+        <v>0.571</v>
       </c>
       <c r="AE9" t="n">
         <v>0</v>
@@ -1693,63 +1693,63 @@
         <v>1</v>
       </c>
       <c r="AI9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.333</v>
+        <v>0.25</v>
       </c>
       <c r="AK9" t="n">
         <v>9</v>
       </c>
       <c r="AL9" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.474</v>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>100:30</t>
+          <t>118:33</t>
         </is>
       </c>
       <c r="AO9" t="n">
-        <v>42.64</v>
+        <v>53.08</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.657</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.638</v>
+        <v>0.552</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.126</v>
+        <v>0.98</v>
       </c>
       <c r="AS9" t="n">
+        <v>0.113</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>3.167</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>7.333</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>0.203</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>0.043</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>0.121</v>
+      </c>
+      <c r="BA9" t="n">
         <v>0.117</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>0.057</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>7</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>0.195</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>0.099</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>0.124</v>
       </c>
     </row>
     <row r="10">
@@ -1759,40 +1759,40 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C10" t="n">
-        <v>72</v>
+        <v>87</v>
       </c>
       <c r="D10" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="E10" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="F10" t="n">
         <v>8</v>
       </c>
       <c r="G10" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="H10" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="I10" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="J10" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="K10" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="N10" t="n">
         <v>3</v>
@@ -1801,49 +1801,49 @@
         <v>3</v>
       </c>
       <c r="P10" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="Q10" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="R10" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="U10" t="n">
         <v>7</v>
       </c>
       <c r="V10" t="n">
+        <v>8</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="n">
         <v>4</v>
       </c>
-      <c r="W10" t="n">
+      <c r="Y10" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>19</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0.632</v>
+      </c>
+      <c r="AB10" t="n">
         <v>7</v>
       </c>
-      <c r="X10" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>15</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>0.667</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>4</v>
-      </c>
       <c r="AC10" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.333</v>
+        <v>0.438</v>
       </c>
       <c r="AE10" t="n">
         <v>3</v>
@@ -1867,54 +1867,54 @@
         <v>8</v>
       </c>
       <c r="AL10" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.381</v>
+        <v>0.333</v>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>126:40</t>
+          <t>160:25</t>
         </is>
       </c>
       <c r="AO10" t="n">
-        <v>79.36</v>
+        <v>98.44</v>
       </c>
       <c r="AP10" t="n">
-        <v>0.492</v>
+        <v>0.486</v>
       </c>
       <c r="AQ10" t="n">
         <v>0.534</v>
       </c>
       <c r="AR10" t="n">
-        <v>0.907</v>
+        <v>0.884</v>
       </c>
       <c r="AS10" t="n">
-        <v>0.151</v>
+        <v>0.173</v>
       </c>
       <c r="AT10" t="n">
-        <v>0.237</v>
+        <v>0.271</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.167</v>
+        <v>1.059</v>
       </c>
       <c r="AV10" t="n">
-        <v>4.917</v>
+        <v>4.118</v>
       </c>
       <c r="AW10" t="n">
-        <v>6.083</v>
+        <v>5.176</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.287</v>
+        <v>0.279</v>
       </c>
       <c r="AY10" t="n">
-        <v>0.032</v>
+        <v>0.031</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.126</v>
+        <v>0.108</v>
       </c>
       <c r="BA10" t="n">
-        <v>0.108</v>
+        <v>0.118</v>
       </c>
     </row>
     <row r="11">
@@ -1924,7 +1924,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C11" t="n">
         <v>10</v>
@@ -1939,7 +1939,7 @@
         <v>1</v>
       </c>
       <c r="G11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H11" t="n">
         <v>3</v>
@@ -1978,7 +1978,7 @@
         <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="U11" t="n">
         <v>2</v>
@@ -2023,7 +2023,7 @@
         <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AJ11" t="n">
         <v>0</v>
@@ -2039,47 +2039,47 @@
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>38:14</t>
+          <t>39:50</t>
         </is>
       </c>
       <c r="AO11" t="n">
-        <v>16.76</v>
+        <v>17.76</v>
       </c>
       <c r="AP11" t="n">
-        <v>0.25</v>
+        <v>0.233</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0.317</v>
+        <v>0.298</v>
       </c>
       <c r="AR11" t="n">
-        <v>0.597</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="AS11" t="n">
-        <v>0.06</v>
+        <v>0.056</v>
       </c>
       <c r="AT11" t="n">
-        <v>0.214</v>
+        <v>0.2</v>
       </c>
       <c r="AU11" t="n">
         <v>1</v>
       </c>
       <c r="AV11" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AW11" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.201</v>
+        <v>0.202</v>
       </c>
       <c r="AY11" t="n">
-        <v>0.027</v>
+        <v>0.025</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.052</v>
+        <v>0.051</v>
       </c>
       <c r="BA11" t="n">
-        <v>0.007</v>
+        <v>0.006</v>
       </c>
     </row>
     <row r="12">
@@ -2089,7 +2089,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C12" t="n">
         <v>2</v>
@@ -2113,7 +2113,7 @@
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K12" t="n">
         <v>1</v>
@@ -2122,7 +2122,7 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -2137,13 +2137,13 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>-5</v>
+        <v>-3</v>
       </c>
       <c r="U12" t="n">
         <v>0</v>
@@ -2204,7 +2204,7 @@
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>24:09</t>
+          <t>26:10</t>
         </is>
       </c>
       <c r="AO12" t="n">
@@ -2235,16 +2235,16 @@
         <v>0</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.133</v>
+        <v>0.121</v>
       </c>
       <c r="AY12" t="n">
         <v>0</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.041</v>
+        <v>0.039</v>
       </c>
       <c r="BA12" t="n">
-        <v>0</v>
+        <v>0.011</v>
       </c>
     </row>
     <row r="13">
@@ -2254,40 +2254,40 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C13" t="n">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="D13" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E13" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F13" t="n">
         <v>11</v>
       </c>
       <c r="G13" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="H13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J13" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="K13" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L13" t="n">
         <v>6</v>
       </c>
       <c r="M13" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N13" t="n">
         <v>1</v>
@@ -2296,49 +2296,49 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="Q13" t="n">
         <v>2</v>
       </c>
       <c r="R13" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="U13" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="V13" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="W13" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="X13" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y13" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Z13" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AA13" t="n">
-        <v>0.1</v>
+        <v>0.308</v>
       </c>
       <c r="AB13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC13" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AD13" t="n">
-        <v>0.571</v>
+        <v>0.6</v>
       </c>
       <c r="AE13" t="n">
         <v>0</v>
@@ -2362,54 +2362,54 @@
         <v>9</v>
       </c>
       <c r="AL13" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.474</v>
+        <v>0.391</v>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>123:53</t>
+          <t>149:02</t>
         </is>
       </c>
       <c r="AO13" t="n">
-        <v>64.95999999999999</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="AP13" t="n">
-        <v>0.531</v>
+        <v>0.527</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0.5679999999999999</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="AR13" t="n">
-        <v>0.908</v>
+        <v>0.89</v>
       </c>
       <c r="AS13" t="n">
-        <v>0.2</v>
+        <v>0.209</v>
       </c>
       <c r="AT13" t="n">
-        <v>0.167</v>
+        <v>0.161</v>
       </c>
       <c r="AU13" t="n">
-        <v>2.308</v>
+        <v>2.188</v>
       </c>
       <c r="AV13" t="n">
-        <v>3.692</v>
+        <v>3.5</v>
       </c>
       <c r="AW13" t="n">
-        <v>6</v>
+        <v>5.688</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.24</v>
+        <v>0.233</v>
       </c>
       <c r="AY13" t="n">
-        <v>0.049</v>
+        <v>0.041</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.112</v>
+        <v>0.103</v>
       </c>
       <c r="BA13" t="n">
-        <v>0.222</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="14">
@@ -2419,162 +2419,162 @@
         </is>
       </c>
       <c r="B14" t="n">
+        <v>6</v>
+      </c>
+      <c r="C14" t="n">
+        <v>45</v>
+      </c>
+      <c r="D14" t="n">
+        <v>11</v>
+      </c>
+      <c r="E14" t="n">
+        <v>23</v>
+      </c>
+      <c r="F14" t="n">
+        <v>6</v>
+      </c>
+      <c r="G14" t="n">
+        <v>19</v>
+      </c>
+      <c r="H14" t="n">
         <v>5</v>
       </c>
-      <c r="C14" t="n">
-        <v>32</v>
-      </c>
-      <c r="D14" t="n">
+      <c r="I14" t="n">
+        <v>8</v>
+      </c>
+      <c r="J14" t="n">
         <v>7</v>
       </c>
-      <c r="E14" t="n">
-        <v>16</v>
-      </c>
-      <c r="F14" t="n">
-        <v>5</v>
-      </c>
-      <c r="G14" t="n">
+      <c r="K14" t="n">
+        <v>25</v>
+      </c>
+      <c r="L14" t="n">
+        <v>14</v>
+      </c>
+      <c r="M14" t="n">
+        <v>4</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1</v>
+      </c>
+      <c r="P14" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
         <v>15</v>
       </c>
-      <c r="H14" t="n">
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>45</v>
+      </c>
+      <c r="U14" t="n">
+        <v>7</v>
+      </c>
+      <c r="V14" t="n">
+        <v>6</v>
+      </c>
+      <c r="W14" t="n">
+        <v>6</v>
+      </c>
+      <c r="X14" t="n">
         <v>3</v>
       </c>
-      <c r="I14" t="n">
-        <v>6</v>
-      </c>
-      <c r="J14" t="n">
-        <v>4</v>
-      </c>
-      <c r="K14" t="n">
-        <v>20</v>
-      </c>
-      <c r="L14" t="n">
-        <v>9</v>
-      </c>
-      <c r="M14" t="n">
-        <v>3</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
-      <c r="P14" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" t="n">
-        <v>13</v>
-      </c>
-      <c r="S14" t="n">
-        <v>0</v>
-      </c>
-      <c r="T14" t="n">
-        <v>29</v>
-      </c>
-      <c r="U14" t="n">
-        <v>3</v>
-      </c>
-      <c r="V14" t="n">
-        <v>2</v>
-      </c>
-      <c r="W14" t="n">
-        <v>3</v>
-      </c>
-      <c r="X14" t="n">
-        <v>2</v>
-      </c>
       <c r="Y14" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="Z14" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.375</v>
+        <v>0.583</v>
       </c>
       <c r="AB14" t="n">
         <v>2</v>
       </c>
       <c r="AC14" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AD14" t="n">
-        <v>0.5</v>
+        <v>0.333</v>
       </c>
       <c r="AE14" t="n">
         <v>2</v>
       </c>
       <c r="AF14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG14" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="AH14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0.333</v>
+        <v>0.375</v>
       </c>
       <c r="AK14" t="n">
         <v>3</v>
       </c>
       <c r="AL14" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.333</v>
+        <v>0.273</v>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>110:33</t>
+          <t>138:31</t>
         </is>
       </c>
       <c r="AO14" t="n">
-        <v>37.64</v>
+        <v>51.52</v>
       </c>
       <c r="AP14" t="n">
-        <v>0.468</v>
+        <v>0.476</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0.476</v>
+        <v>0.494</v>
       </c>
       <c r="AR14" t="n">
-        <v>0.85</v>
+        <v>0.873</v>
       </c>
       <c r="AS14" t="n">
-        <v>0.106</v>
+        <v>0.116</v>
       </c>
       <c r="AT14" t="n">
-        <v>0.097</v>
+        <v>0.119</v>
       </c>
       <c r="AU14" t="n">
-        <v>1</v>
+        <v>1.167</v>
       </c>
       <c r="AV14" t="n">
-        <v>7.75</v>
+        <v>7</v>
       </c>
       <c r="AW14" t="n">
-        <v>8.75</v>
+        <v>8.167</v>
       </c>
       <c r="AX14" t="n">
-        <v>0.156</v>
+        <v>0.169</v>
       </c>
       <c r="AY14" t="n">
-        <v>0.083</v>
+        <v>0.102</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0.18</v>
+        <v>0.184</v>
       </c>
       <c r="BA14" t="n">
-        <v>0.028</v>
+        <v>0.042</v>
       </c>
     </row>
     <row r="15">
@@ -2584,16 +2584,16 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C15" t="n">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="D15" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E15" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -2611,73 +2611,73 @@
         <v>3</v>
       </c>
       <c r="K15" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="L15" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O15" t="n">
         <v>2</v>
       </c>
       <c r="P15" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Q15" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="R15" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="U15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="V15" t="n">
         <v>8</v>
       </c>
       <c r="W15" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="X15" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y15" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="Z15" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.636</v>
+        <v>0.615</v>
       </c>
       <c r="AB15" t="n">
         <v>5</v>
       </c>
       <c r="AC15" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AD15" t="n">
-        <v>0.357</v>
+        <v>0.312</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AH15" t="n">
         <v>0</v>
@@ -2699,47 +2699,47 @@
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>110:25</t>
+          <t>128:57</t>
         </is>
       </c>
       <c r="AO15" t="n">
-        <v>48.04</v>
+        <v>58.04</v>
       </c>
       <c r="AP15" t="n">
-        <v>0.514</v>
+        <v>0.5</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0.556</v>
+        <v>0.539</v>
       </c>
       <c r="AR15" t="n">
-        <v>1.02</v>
+        <v>0.948</v>
       </c>
       <c r="AS15" t="n">
-        <v>0.083</v>
+        <v>0.121</v>
       </c>
       <c r="AT15" t="n">
-        <v>0.297</v>
+        <v>0.25</v>
       </c>
       <c r="AU15" t="n">
-        <v>0.75</v>
+        <v>0.429</v>
       </c>
       <c r="AV15" t="n">
-        <v>9.25</v>
+        <v>6.286</v>
       </c>
       <c r="AW15" t="n">
-        <v>10</v>
+        <v>6.714</v>
       </c>
       <c r="AX15" t="n">
-        <v>0.199</v>
+        <v>0.204</v>
       </c>
       <c r="AY15" t="n">
-        <v>0.12</v>
+        <v>0.133</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0.135</v>
+        <v>0.158</v>
       </c>
       <c r="BA15" t="n">
-        <v>0.022</v>
+        <v>0.019</v>
       </c>
     </row>
     <row r="16">
@@ -2749,7 +2749,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C16" t="n">
         <v>16</v>
@@ -2758,13 +2758,13 @@
         <v>4</v>
       </c>
       <c r="E16" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F16" t="n">
         <v>2</v>
       </c>
       <c r="G16" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H16" t="n">
         <v>2</v>
@@ -2803,7 +2803,7 @@
         <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U16" t="n">
         <v>2</v>
@@ -2821,10 +2821,10 @@
         <v>3</v>
       </c>
       <c r="Z16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.429</v>
+        <v>0.375</v>
       </c>
       <c r="AB16" t="n">
         <v>1</v>
@@ -2848,10 +2848,10 @@
         <v>1</v>
       </c>
       <c r="AI16" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.067</v>
       </c>
       <c r="AK16" t="n">
         <v>1</v>
@@ -2864,47 +2864,47 @@
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>76:42</t>
+          <t>83:20</t>
         </is>
       </c>
       <c r="AO16" t="n">
-        <v>32.2</v>
+        <v>34.2</v>
       </c>
       <c r="AP16" t="n">
-        <v>0.259</v>
+        <v>0.241</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0.274</v>
+        <v>0.256</v>
       </c>
       <c r="AR16" t="n">
-        <v>0.497</v>
+        <v>0.468</v>
       </c>
       <c r="AS16" t="n">
-        <v>0.093</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="AT16" t="n">
-        <v>0.074</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="AU16" t="n">
         <v>0.667</v>
       </c>
       <c r="AV16" t="n">
-        <v>9</v>
+        <v>9.667</v>
       </c>
       <c r="AW16" t="n">
-        <v>9.667</v>
+        <v>10.333</v>
       </c>
       <c r="AX16" t="n">
-        <v>0.192</v>
+        <v>0.186</v>
       </c>
       <c r="AY16" t="n">
-        <v>0.053</v>
+        <v>0.048</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0.143</v>
+        <v>0.135</v>
       </c>
       <c r="BA16" t="n">
-        <v>0.013</v>
+        <v>0.011</v>
       </c>
     </row>
     <row r="17">
@@ -2914,16 +2914,16 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C17" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="D17" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E17" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
@@ -2941,10 +2941,10 @@
         <v>2</v>
       </c>
       <c r="K17" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="L17" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="M17" t="n">
         <v>1</v>
@@ -2956,19 +2956,19 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q17" t="n">
         <v>2</v>
       </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
       <c r="R17" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="U17" t="n">
         <v>4</v>
@@ -2983,22 +2983,22 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="Z17" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AA17" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.55</v>
       </c>
       <c r="AB17" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AC17" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AD17" t="n">
-        <v>0.714</v>
+        <v>0.7</v>
       </c>
       <c r="AE17" t="n">
         <v>3</v>
@@ -3029,47 +3029,47 @@
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>85:58</t>
+          <t>107:35</t>
         </is>
       </c>
       <c r="AO17" t="n">
-        <v>34.08</v>
+        <v>44.08</v>
       </c>
       <c r="AP17" t="n">
-        <v>0.586</v>
+        <v>0.583</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0.623</v>
+        <v>0.614</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.174</v>
+        <v>1.089</v>
       </c>
       <c r="AS17" t="n">
-        <v>0.059</v>
+        <v>0.113</v>
       </c>
       <c r="AT17" t="n">
-        <v>0.207</v>
+        <v>0.167</v>
       </c>
       <c r="AU17" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="AV17" t="n">
-        <v>14.5</v>
+        <v>7.2</v>
       </c>
       <c r="AW17" t="n">
-        <v>15.5</v>
+        <v>7.6</v>
       </c>
       <c r="AX17" t="n">
-        <v>0.182</v>
+        <v>0.186</v>
       </c>
       <c r="AY17" t="n">
-        <v>0.154</v>
+        <v>0.141</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0.266</v>
+        <v>0.256</v>
       </c>
       <c r="BA17" t="n">
-        <v>0.014</v>
+        <v>0.012</v>
       </c>
     </row>
     <row r="18">
@@ -3079,7 +3079,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C18" t="n">
         <v>41</v>
@@ -3088,13 +3088,13 @@
         <v>10</v>
       </c>
       <c r="E18" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F18" t="n">
         <v>6</v>
       </c>
       <c r="G18" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H18" t="n">
         <v>3</v>
@@ -3127,13 +3127,13 @@
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="S18" t="n">
         <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="U18" t="n">
         <v>0</v>
@@ -3151,10 +3151,10 @@
         <v>7</v>
       </c>
       <c r="Z18" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA18" t="n">
-        <v>0.7</v>
+        <v>0.636</v>
       </c>
       <c r="AB18" t="n">
         <v>2</v>
@@ -3178,7 +3178,7 @@
         <v>0</v>
       </c>
       <c r="AI18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AJ18" t="n">
         <v>0</v>
@@ -3187,54 +3187,54 @@
         <v>6</v>
       </c>
       <c r="AL18" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AM18" t="n">
-        <v>0.75</v>
+        <v>0.667</v>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>88:38</t>
+          <t>100:29</t>
         </is>
       </c>
       <c r="AO18" t="n">
-        <v>29.64</v>
+        <v>32.64</v>
       </c>
       <c r="AP18" t="n">
-        <v>0.731</v>
+        <v>0.655</v>
       </c>
       <c r="AQ18" t="n">
-        <v>0.716</v>
+        <v>0.648</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.383</v>
+        <v>1.256</v>
       </c>
       <c r="AS18" t="n">
-        <v>0.034</v>
+        <v>0.031</v>
       </c>
       <c r="AT18" t="n">
-        <v>0.115</v>
+        <v>0.103</v>
       </c>
       <c r="AU18" t="n">
         <v>2</v>
       </c>
       <c r="AV18" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="AW18" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="AX18" t="n">
-        <v>0.153</v>
+        <v>0.148</v>
       </c>
       <c r="AY18" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0.168</v>
+        <v>0.152</v>
       </c>
       <c r="BA18" t="n">
-        <v>0.014</v>
+        <v>0.012</v>
       </c>
     </row>
     <row r="19">
@@ -3244,7 +3244,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C19" t="n">
         <v>0</v>
@@ -3409,7 +3409,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C20" t="n">
         <v>0</v>
@@ -3436,10 +3436,10 @@
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="L20" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="M20" t="n">
         <v>0</v>
@@ -3574,159 +3574,159 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C21" t="n">
-        <v>422</v>
+        <v>493</v>
       </c>
       <c r="D21" t="n">
-        <v>96</v>
+        <v>118</v>
       </c>
       <c r="E21" t="n">
-        <v>202</v>
+        <v>243</v>
       </c>
       <c r="F21" t="n">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="G21" t="n">
-        <v>147</v>
+        <v>174</v>
       </c>
       <c r="H21" t="n">
+        <v>62</v>
+      </c>
+      <c r="I21" t="n">
+        <v>92</v>
+      </c>
+      <c r="J21" t="n">
+        <v>95</v>
+      </c>
+      <c r="K21" t="n">
+        <v>167</v>
+      </c>
+      <c r="L21" t="n">
+        <v>88</v>
+      </c>
+      <c r="M21" t="n">
+        <v>40</v>
+      </c>
+      <c r="N21" t="n">
+        <v>9</v>
+      </c>
+      <c r="O21" t="n">
+        <v>8</v>
+      </c>
+      <c r="P21" t="n">
+        <v>71</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>27</v>
+      </c>
+      <c r="R21" t="n">
+        <v>127</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>401</v>
+      </c>
+      <c r="U21" t="n">
+        <v>42</v>
+      </c>
+      <c r="V21" t="n">
         <v>53</v>
       </c>
-      <c r="I21" t="n">
-        <v>80</v>
-      </c>
-      <c r="J21" t="n">
-        <v>79</v>
-      </c>
-      <c r="K21" t="n">
-        <v>141</v>
-      </c>
-      <c r="L21" t="n">
-        <v>72</v>
-      </c>
-      <c r="M21" t="n">
+      <c r="W21" t="n">
+        <v>65</v>
+      </c>
+      <c r="X21" t="n">
         <v>29</v>
       </c>
-      <c r="N21" t="n">
-        <v>8</v>
-      </c>
-      <c r="O21" t="n">
-        <v>6</v>
-      </c>
-      <c r="P21" t="n">
+      <c r="Y21" t="n">
+        <v>68</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>128</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>0.531</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>37</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>78</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>0.474</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>13</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>37</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>0.351</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>13</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>51</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>0.255</v>
+      </c>
+      <c r="AK21" t="n">
         <v>52</v>
       </c>
-      <c r="Q21" t="n">
-        <v>16</v>
-      </c>
-      <c r="R21" t="n">
-        <v>104</v>
-      </c>
-      <c r="S21" t="n">
-        <v>0</v>
-      </c>
-      <c r="T21" t="n">
-        <v>354</v>
-      </c>
-      <c r="U21" t="n">
-        <v>34</v>
-      </c>
-      <c r="V21" t="n">
-        <v>43</v>
-      </c>
-      <c r="W21" t="n">
-        <v>44</v>
-      </c>
-      <c r="X21" t="n">
-        <v>20</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>54</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>104</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>0.519</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>30</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>64</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>0.469</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>12</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>34</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>0.353</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>11</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>44</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>48</v>
-      </c>
       <c r="AL21" t="n">
-        <v>103</v>
+        <v>123</v>
       </c>
       <c r="AM21" t="n">
-        <v>0.466</v>
+        <v>0.423</v>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>1000:00</t>
+          <t>1200:00</t>
         </is>
       </c>
       <c r="AO21" t="n">
-        <v>436.2</v>
+        <v>528.48</v>
       </c>
       <c r="AP21" t="n">
-        <v>0.529</v>
+        <v>0.517</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0.549</v>
+        <v>0.539</v>
       </c>
       <c r="AR21" t="n">
-        <v>0.967</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="AS21" t="n">
-        <v>0.119</v>
+        <v>0.134</v>
       </c>
       <c r="AT21" t="n">
-        <v>0.152</v>
+        <v>0.149</v>
       </c>
       <c r="AU21" t="n">
-        <v>1.519</v>
+        <v>1.338</v>
       </c>
       <c r="AV21" t="n">
-        <v>6.712</v>
+        <v>5.873</v>
       </c>
       <c r="AW21" t="n">
-        <v>8.231</v>
+        <v>7.211</v>
       </c>
       <c r="AX21" t="n">
         <v>0.2</v>
       </c>
       <c r="AY21" t="n">
-        <v>0.073</v>
+        <v>0.074</v>
       </c>
       <c r="AZ21" t="n">
-        <v>0.14</v>
+        <v>0.142</v>
       </c>
       <c r="BA21" t="n">
         <v>0</v>
@@ -3739,159 +3739,159 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C22" t="n">
-        <v>359</v>
+        <v>415</v>
       </c>
       <c r="D22" t="n">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="E22" t="n">
-        <v>185</v>
+        <v>215</v>
       </c>
       <c r="F22" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="G22" t="n">
-        <v>127</v>
+        <v>151</v>
       </c>
       <c r="H22" t="n">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="I22" t="n">
-        <v>99</v>
+        <v>120</v>
       </c>
       <c r="J22" t="n">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="K22" t="n">
-        <v>124</v>
+        <v>150</v>
       </c>
       <c r="L22" t="n">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="M22" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="N22" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O22" t="n">
         <v>8</v>
       </c>
       <c r="P22" t="n">
-        <v>60</v>
+        <v>79</v>
       </c>
       <c r="Q22" t="n">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="R22" t="n">
-        <v>102</v>
+        <v>121</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>245</v>
+        <v>269</v>
       </c>
       <c r="U22" t="n">
+        <v>45</v>
+      </c>
+      <c r="V22" t="n">
         <v>40</v>
       </c>
-      <c r="V22" t="n">
+      <c r="W22" t="n">
+        <v>74</v>
+      </c>
+      <c r="X22" t="n">
+        <v>38</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>64</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>107</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>0.598</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>20</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>71</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>0.282</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>13</v>
+      </c>
+      <c r="AF22" t="n">
         <v>37</v>
       </c>
-      <c r="W22" t="n">
-        <v>62</v>
-      </c>
-      <c r="X22" t="n">
-        <v>33</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>55</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>94</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>0.585</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>17</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>61</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>0.279</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>11</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>30</v>
-      </c>
       <c r="AG22" t="n">
-        <v>0.367</v>
+        <v>0.351</v>
       </c>
       <c r="AH22" t="n">
         <v>5</v>
       </c>
       <c r="AI22" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0.172</v>
+        <v>0.161</v>
       </c>
       <c r="AK22" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="AL22" t="n">
-        <v>98</v>
+        <v>120</v>
       </c>
       <c r="AM22" t="n">
-        <v>0.337</v>
+        <v>0.317</v>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>1000:00</t>
+          <t>1200:00</t>
         </is>
       </c>
       <c r="AO22" t="n">
-        <v>415.56</v>
+        <v>497.8</v>
       </c>
       <c r="AP22" t="n">
-        <v>0.449</v>
+        <v>0.441</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0.505</v>
+        <v>0.495</v>
       </c>
       <c r="AR22" t="n">
-        <v>0.864</v>
+        <v>0.834</v>
       </c>
       <c r="AS22" t="n">
-        <v>0.144</v>
+        <v>0.159</v>
       </c>
       <c r="AT22" t="n">
-        <v>0.253</v>
+        <v>0.251</v>
       </c>
       <c r="AU22" t="n">
-        <v>0.983</v>
+        <v>0.848</v>
       </c>
       <c r="AV22" t="n">
-        <v>5.2</v>
+        <v>4.633</v>
       </c>
       <c r="AW22" t="n">
-        <v>6.183</v>
+        <v>5.481</v>
       </c>
       <c r="AX22" t="n">
         <v>0.2</v>
       </c>
       <c r="AY22" t="n">
-        <v>0.06</v>
+        <v>0.058</v>
       </c>
       <c r="AZ22" t="n">
-        <v>0.127</v>
+        <v>0.126</v>
       </c>
       <c r="BA22" t="n">
         <v>0</v>
@@ -3963,162 +3963,162 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C24" t="n">
-        <v>10.6</v>
+        <v>11.5</v>
       </c>
       <c r="D24" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="F24" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G24" t="n">
+        <v>6.667</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="K24" t="n">
+        <v>1.167</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="R24" t="n">
+        <v>2.667</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>43</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X24" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="AG24" t="n">
         <v>0.4</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="F24" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="G24" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="K24" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="R24" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="S24" t="n">
-        <v>0</v>
-      </c>
-      <c r="T24" t="n">
-        <v>32</v>
-      </c>
-      <c r="U24" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="V24" t="n">
-        <v>0</v>
-      </c>
-      <c r="W24" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="X24" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>0.5</v>
       </c>
       <c r="AH24" t="n">
         <v>1</v>
       </c>
       <c r="AI24" t="n">
-        <v>2.4</v>
+        <v>2.167</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0.417</v>
+        <v>0.462</v>
       </c>
       <c r="AK24" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="AL24" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="AM24" t="n">
-        <v>0.55</v>
+        <v>0.556</v>
       </c>
       <c r="AN24" t="inlineStr">
         <is>
-          <t>22:51</t>
+          <t>24:31</t>
         </is>
       </c>
       <c r="AO24" t="n">
-        <v>7.976</v>
+        <v>8.553000000000001</v>
       </c>
       <c r="AP24" t="n">
-        <v>0.722</v>
+        <v>0.744</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0.719</v>
+        <v>0.745</v>
       </c>
       <c r="AR24" t="n">
-        <v>1.329</v>
+        <v>1.345</v>
       </c>
       <c r="AS24" t="n">
-        <v>0.075</v>
+        <v>0.097</v>
       </c>
       <c r="AT24" t="n">
-        <v>0.028</v>
+        <v>0.044</v>
       </c>
       <c r="AU24" t="n">
-        <v>1.333</v>
+        <v>0.8</v>
       </c>
       <c r="AV24" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AW24" t="n">
-        <v>13.333</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AX24" t="n">
-        <v>0.16</v>
+        <v>0.158</v>
       </c>
       <c r="AY24" t="n">
-        <v>0.027</v>
+        <v>0.021</v>
       </c>
       <c r="AZ24" t="n">
-        <v>0.052</v>
+        <v>0.049</v>
       </c>
       <c r="BA24" t="n">
-        <v>0.029</v>
+        <v>0.025</v>
       </c>
     </row>
     <row r="25">
@@ -4128,91 +4128,91 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C25" t="n">
-        <v>9.6</v>
+        <v>8.667</v>
       </c>
       <c r="D25" t="n">
-        <v>1.6</v>
+        <v>1.667</v>
       </c>
       <c r="E25" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="F25" t="n">
-        <v>2</v>
+        <v>1.667</v>
       </c>
       <c r="G25" t="n">
-        <v>3.8</v>
+        <v>3.833</v>
       </c>
       <c r="H25" t="n">
-        <v>0.4</v>
+        <v>0.333</v>
       </c>
       <c r="I25" t="n">
-        <v>1.2</v>
+        <v>1.167</v>
       </c>
       <c r="J25" t="n">
-        <v>3.4</v>
+        <v>3.167</v>
       </c>
       <c r="K25" t="n">
-        <v>2</v>
+        <v>2.333</v>
       </c>
       <c r="L25" t="n">
-        <v>0.6</v>
+        <v>0.833</v>
       </c>
       <c r="M25" t="n">
-        <v>0.8</v>
+        <v>1.167</v>
       </c>
       <c r="N25" t="n">
         <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P25" t="n">
         <v>1</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>0.167</v>
       </c>
       <c r="R25" t="n">
-        <v>1.8</v>
+        <v>1.833</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="U25" t="n">
-        <v>0.4</v>
+        <v>0.333</v>
       </c>
       <c r="V25" t="n">
-        <v>0.4</v>
+        <v>0.333</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>0.167</v>
       </c>
       <c r="Y25" t="n">
         <v>1</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.2</v>
+        <v>2.333</v>
       </c>
       <c r="AA25" t="n">
-        <v>0.455</v>
+        <v>0.429</v>
       </c>
       <c r="AB25" t="n">
-        <v>0.6</v>
+        <v>0.667</v>
       </c>
       <c r="AC25" t="n">
-        <v>1</v>
+        <v>1.167</v>
       </c>
       <c r="AD25" t="n">
-        <v>0.6</v>
+        <v>0.571</v>
       </c>
       <c r="AE25" t="n">
         <v>0</v>
@@ -4224,66 +4224,66 @@
         <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>0.2</v>
+        <v>0.167</v>
       </c>
       <c r="AI25" t="n">
-        <v>0.6</v>
+        <v>0.667</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0.333</v>
+        <v>0.25</v>
       </c>
       <c r="AK25" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="AL25" t="n">
-        <v>3.2</v>
+        <v>3.167</v>
       </c>
       <c r="AM25" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.474</v>
       </c>
       <c r="AN25" t="inlineStr">
         <is>
-          <t>20:06</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="AO25" t="n">
-        <v>8.528</v>
+        <v>8.847</v>
       </c>
       <c r="AP25" t="n">
-        <v>0.657</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="AQ25" t="n">
-        <v>0.638</v>
+        <v>0.552</v>
       </c>
       <c r="AR25" t="n">
-        <v>1.126</v>
+        <v>0.98</v>
       </c>
       <c r="AS25" t="n">
+        <v>0.113</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>3.167</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>7.333</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>0.203</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>0.043</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>0.121</v>
+      </c>
+      <c r="BA25" t="n">
         <v>0.117</v>
-      </c>
-      <c r="AT25" t="n">
-        <v>0.057</v>
-      </c>
-      <c r="AU25" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AV25" t="n">
-        <v>7</v>
-      </c>
-      <c r="AW25" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="AX25" t="n">
-        <v>0.195</v>
-      </c>
-      <c r="AY25" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="AZ25" t="n">
-        <v>0.099</v>
-      </c>
-      <c r="BA25" t="n">
-        <v>0.124</v>
       </c>
     </row>
     <row r="26">
@@ -4293,97 +4293,97 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C26" t="n">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="D26" t="n">
-        <v>3.4</v>
+        <v>3.667</v>
       </c>
       <c r="E26" t="n">
-        <v>7.2</v>
+        <v>7.333</v>
       </c>
       <c r="F26" t="n">
-        <v>1.6</v>
+        <v>1.333</v>
       </c>
       <c r="G26" t="n">
-        <v>4.6</v>
+        <v>4.333</v>
       </c>
       <c r="H26" t="n">
-        <v>2.8</v>
+        <v>3.167</v>
       </c>
       <c r="I26" t="n">
-        <v>3.8</v>
+        <v>4.333</v>
       </c>
       <c r="J26" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="K26" t="n">
-        <v>3.2</v>
+        <v>2.833</v>
       </c>
       <c r="L26" t="n">
-        <v>0.8</v>
+        <v>0.833</v>
       </c>
       <c r="M26" t="n">
-        <v>1.4</v>
+        <v>1.333</v>
       </c>
       <c r="N26" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="O26" t="n">
         <v>3</v>
       </c>
       <c r="P26" t="n">
-        <v>2.4</v>
+        <v>2.833</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.8</v>
+        <v>1.333</v>
       </c>
       <c r="R26" t="n">
-        <v>2.6</v>
+        <v>2.833</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="U26" t="n">
-        <v>1.4</v>
+        <v>1.167</v>
       </c>
       <c r="V26" t="n">
-        <v>0.8</v>
+        <v>1.333</v>
       </c>
       <c r="W26" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="X26" t="n">
-        <v>0.6</v>
+        <v>0.667</v>
       </c>
       <c r="Y26" t="n">
         <v>2</v>
       </c>
       <c r="Z26" t="n">
-        <v>3</v>
+        <v>3.167</v>
       </c>
       <c r="AA26" t="n">
-        <v>0.667</v>
+        <v>0.632</v>
       </c>
       <c r="AB26" t="n">
-        <v>0.8</v>
+        <v>1.167</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.4</v>
+        <v>2.667</v>
       </c>
       <c r="AD26" t="n">
-        <v>0.333</v>
+        <v>0.438</v>
       </c>
       <c r="AE26" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="AG26" t="n">
         <v>0.333</v>
@@ -4392,63 +4392,63 @@
         <v>0</v>
       </c>
       <c r="AI26" t="n">
-        <v>0.4</v>
+        <v>0.333</v>
       </c>
       <c r="AJ26" t="n">
         <v>0</v>
       </c>
       <c r="AK26" t="n">
-        <v>1.6</v>
+        <v>1.333</v>
       </c>
       <c r="AL26" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="AM26" t="n">
-        <v>0.381</v>
+        <v>0.333</v>
       </c>
       <c r="AN26" t="inlineStr">
         <is>
-          <t>25:20</t>
+          <t>26:44</t>
         </is>
       </c>
       <c r="AO26" t="n">
-        <v>15.872</v>
+        <v>16.407</v>
       </c>
       <c r="AP26" t="n">
-        <v>0.492</v>
+        <v>0.486</v>
       </c>
       <c r="AQ26" t="n">
         <v>0.534</v>
       </c>
       <c r="AR26" t="n">
-        <v>0.907</v>
+        <v>0.884</v>
       </c>
       <c r="AS26" t="n">
-        <v>0.151</v>
+        <v>0.173</v>
       </c>
       <c r="AT26" t="n">
-        <v>0.237</v>
+        <v>0.271</v>
       </c>
       <c r="AU26" t="n">
-        <v>1.167</v>
+        <v>1.059</v>
       </c>
       <c r="AV26" t="n">
-        <v>4.917</v>
+        <v>4.118</v>
       </c>
       <c r="AW26" t="n">
-        <v>6.083</v>
+        <v>5.176</v>
       </c>
       <c r="AX26" t="n">
-        <v>0.287</v>
+        <v>0.279</v>
       </c>
       <c r="AY26" t="n">
-        <v>0.032</v>
+        <v>0.031</v>
       </c>
       <c r="AZ26" t="n">
-        <v>0.126</v>
+        <v>0.108</v>
       </c>
       <c r="BA26" t="n">
-        <v>0.108</v>
+        <v>0.118</v>
       </c>
     </row>
     <row r="27">
@@ -4458,37 +4458,37 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C27" t="n">
-        <v>2</v>
+        <v>1.667</v>
       </c>
       <c r="D27" t="n">
-        <v>0.4</v>
+        <v>0.333</v>
       </c>
       <c r="E27" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="F27" t="n">
-        <v>0.2</v>
+        <v>0.167</v>
       </c>
       <c r="G27" t="n">
         <v>1</v>
       </c>
       <c r="H27" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="I27" t="n">
-        <v>0.8</v>
+        <v>0.667</v>
       </c>
       <c r="J27" t="n">
-        <v>0.2</v>
+        <v>0.167</v>
       </c>
       <c r="K27" t="n">
-        <v>0.4</v>
+        <v>0.333</v>
       </c>
       <c r="L27" t="n">
-        <v>0.2</v>
+        <v>0.167</v>
       </c>
       <c r="M27" t="n">
         <v>0</v>
@@ -4500,25 +4500,25 @@
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>0.2</v>
+        <v>0.167</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>1</v>
+        <v>0.833</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="U27" t="n">
-        <v>0.4</v>
+        <v>0.333</v>
       </c>
       <c r="V27" t="n">
-        <v>0.4</v>
+        <v>0.333</v>
       </c>
       <c r="W27" t="n">
         <v>0</v>
@@ -4527,10 +4527,10 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>0.2</v>
+        <v>0.167</v>
       </c>
       <c r="Z27" t="n">
-        <v>0.4</v>
+        <v>0.333</v>
       </c>
       <c r="AA27" t="n">
         <v>0.5</v>
@@ -4539,16 +4539,16 @@
         <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>0.8</v>
+        <v>0.667</v>
       </c>
       <c r="AD27" t="n">
         <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>0.2</v>
+        <v>0.167</v>
       </c>
       <c r="AF27" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="AG27" t="n">
         <v>0.333</v>
@@ -4557,63 +4557,63 @@
         <v>0</v>
       </c>
       <c r="AI27" t="n">
-        <v>0.2</v>
+        <v>0.333</v>
       </c>
       <c r="AJ27" t="n">
         <v>0</v>
       </c>
       <c r="AK27" t="n">
-        <v>0.2</v>
+        <v>0.167</v>
       </c>
       <c r="AL27" t="n">
-        <v>0.8</v>
+        <v>0.667</v>
       </c>
       <c r="AM27" t="n">
         <v>0.25</v>
       </c>
       <c r="AN27" t="inlineStr">
         <is>
-          <t>07:38</t>
+          <t>06:38</t>
         </is>
       </c>
       <c r="AO27" t="n">
-        <v>3.352</v>
+        <v>2.96</v>
       </c>
       <c r="AP27" t="n">
-        <v>0.25</v>
+        <v>0.233</v>
       </c>
       <c r="AQ27" t="n">
-        <v>0.317</v>
+        <v>0.298</v>
       </c>
       <c r="AR27" t="n">
-        <v>0.597</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="AS27" t="n">
-        <v>0.06</v>
+        <v>0.056</v>
       </c>
       <c r="AT27" t="n">
-        <v>0.214</v>
+        <v>0.2</v>
       </c>
       <c r="AU27" t="n">
         <v>1</v>
       </c>
       <c r="AV27" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AW27" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AX27" t="n">
-        <v>0.201</v>
+        <v>0.202</v>
       </c>
       <c r="AY27" t="n">
-        <v>0.027</v>
+        <v>0.025</v>
       </c>
       <c r="AZ27" t="n">
-        <v>0.052</v>
+        <v>0.051</v>
       </c>
       <c r="BA27" t="n">
-        <v>0.007</v>
+        <v>0.006</v>
       </c>
     </row>
     <row r="28">
@@ -4623,22 +4623,22 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C28" t="n">
-        <v>0.4</v>
+        <v>0.333</v>
       </c>
       <c r="D28" t="n">
-        <v>0.2</v>
+        <v>0.167</v>
       </c>
       <c r="E28" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="F28" t="n">
         <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>0.8</v>
+        <v>0.667</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
@@ -4647,16 +4647,16 @@
         <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="K28" t="n">
-        <v>0.2</v>
+        <v>0.167</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>0.167</v>
       </c>
       <c r="N28" t="n">
         <v>0</v>
@@ -4671,13 +4671,13 @@
         <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>-5</v>
+        <v>-3</v>
       </c>
       <c r="U28" t="n">
         <v>0</v>
@@ -4686,16 +4686,16 @@
         <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>0.4</v>
+        <v>0.333</v>
       </c>
       <c r="X28" t="n">
-        <v>0.2</v>
+        <v>0.167</v>
       </c>
       <c r="Y28" t="n">
-        <v>0.2</v>
+        <v>0.167</v>
       </c>
       <c r="Z28" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="AA28" t="n">
         <v>0.333</v>
@@ -4722,7 +4722,7 @@
         <v>0</v>
       </c>
       <c r="AI28" t="n">
-        <v>0.2</v>
+        <v>0.167</v>
       </c>
       <c r="AJ28" t="n">
         <v>0</v>
@@ -4731,18 +4731,18 @@
         <v>0</v>
       </c>
       <c r="AL28" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="AM28" t="n">
         <v>0</v>
       </c>
       <c r="AN28" t="inlineStr">
         <is>
-          <t>04:49</t>
+          <t>04:21</t>
         </is>
       </c>
       <c r="AO28" t="n">
-        <v>1.4</v>
+        <v>1.167</v>
       </c>
       <c r="AP28" t="n">
         <v>0.143</v>
@@ -4769,16 +4769,16 @@
         <v>0</v>
       </c>
       <c r="AX28" t="n">
-        <v>0.133</v>
+        <v>0.121</v>
       </c>
       <c r="AY28" t="n">
         <v>0</v>
       </c>
       <c r="AZ28" t="n">
-        <v>0.041</v>
+        <v>0.039</v>
       </c>
       <c r="BA28" t="n">
-        <v>0</v>
+        <v>0.011</v>
       </c>
     </row>
     <row r="29">
@@ -4788,162 +4788,162 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C29" t="n">
-        <v>11.8</v>
+        <v>11.333</v>
       </c>
       <c r="D29" t="n">
-        <v>1.8</v>
+        <v>2.167</v>
       </c>
       <c r="E29" t="n">
-        <v>5</v>
+        <v>4.833</v>
       </c>
       <c r="F29" t="n">
-        <v>2.2</v>
+        <v>1.833</v>
       </c>
       <c r="G29" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="H29" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="I29" t="n">
-        <v>1.8</v>
+        <v>1.667</v>
       </c>
       <c r="J29" t="n">
-        <v>6</v>
+        <v>5.833</v>
       </c>
       <c r="K29" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="L29" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="M29" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="N29" t="n">
-        <v>0.2</v>
+        <v>0.167</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>2.6</v>
+        <v>2.667</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.4</v>
+        <v>0.333</v>
       </c>
       <c r="R29" t="n">
-        <v>2</v>
+        <v>2.333</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="U29" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="V29" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="W29" t="n">
-        <v>3.2</v>
+        <v>3.333</v>
       </c>
       <c r="X29" t="n">
-        <v>1.2</v>
+        <v>1.333</v>
       </c>
       <c r="Y29" t="n">
-        <v>0.2</v>
+        <v>0.667</v>
       </c>
       <c r="Z29" t="n">
-        <v>2</v>
+        <v>2.167</v>
       </c>
       <c r="AA29" t="n">
-        <v>0.1</v>
+        <v>0.308</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="AD29" t="n">
-        <v>0.571</v>
+        <v>0.6</v>
       </c>
       <c r="AE29" t="n">
         <v>0</v>
       </c>
       <c r="AF29" t="n">
-        <v>0.2</v>
+        <v>0.167</v>
       </c>
       <c r="AG29" t="n">
         <v>0</v>
       </c>
       <c r="AH29" t="n">
-        <v>0.4</v>
+        <v>0.333</v>
       </c>
       <c r="AI29" t="n">
-        <v>0.8</v>
+        <v>0.667</v>
       </c>
       <c r="AJ29" t="n">
         <v>0.5</v>
       </c>
       <c r="AK29" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="AL29" t="n">
-        <v>3.8</v>
+        <v>3.833</v>
       </c>
       <c r="AM29" t="n">
-        <v>0.474</v>
+        <v>0.391</v>
       </c>
       <c r="AN29" t="inlineStr">
         <is>
-          <t>24:46</t>
+          <t>24:50</t>
         </is>
       </c>
       <c r="AO29" t="n">
-        <v>12.992</v>
+        <v>12.733</v>
       </c>
       <c r="AP29" t="n">
-        <v>0.531</v>
+        <v>0.527</v>
       </c>
       <c r="AQ29" t="n">
-        <v>0.5679999999999999</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="AR29" t="n">
-        <v>0.908</v>
+        <v>0.89</v>
       </c>
       <c r="AS29" t="n">
-        <v>0.2</v>
+        <v>0.209</v>
       </c>
       <c r="AT29" t="n">
-        <v>0.167</v>
+        <v>0.161</v>
       </c>
       <c r="AU29" t="n">
-        <v>2.308</v>
+        <v>2.188</v>
       </c>
       <c r="AV29" t="n">
-        <v>3.692</v>
+        <v>3.5</v>
       </c>
       <c r="AW29" t="n">
-        <v>6</v>
+        <v>5.687</v>
       </c>
       <c r="AX29" t="n">
-        <v>0.24</v>
+        <v>0.233</v>
       </c>
       <c r="AY29" t="n">
-        <v>0.049</v>
+        <v>0.041</v>
       </c>
       <c r="AZ29" t="n">
-        <v>0.112</v>
+        <v>0.103</v>
       </c>
       <c r="BA29" t="n">
-        <v>0.222</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="30">
@@ -4953,162 +4953,162 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C30" t="n">
-        <v>6.4</v>
+        <v>7.5</v>
       </c>
       <c r="D30" t="n">
-        <v>1.4</v>
+        <v>1.833</v>
       </c>
       <c r="E30" t="n">
-        <v>3.2</v>
+        <v>3.833</v>
       </c>
       <c r="F30" t="n">
         <v>1</v>
       </c>
       <c r="G30" t="n">
-        <v>3</v>
+        <v>3.167</v>
       </c>
       <c r="H30" t="n">
-        <v>0.6</v>
+        <v>0.833</v>
       </c>
       <c r="I30" t="n">
-        <v>1.2</v>
+        <v>1.333</v>
       </c>
       <c r="J30" t="n">
-        <v>0.8</v>
+        <v>1.167</v>
       </c>
       <c r="K30" t="n">
-        <v>4</v>
+        <v>4.167</v>
       </c>
       <c r="L30" t="n">
-        <v>1.8</v>
+        <v>2.333</v>
       </c>
       <c r="M30" t="n">
-        <v>0.6</v>
+        <v>0.667</v>
       </c>
       <c r="N30" t="n">
         <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P30" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="U30" t="n">
-        <v>0.6</v>
+        <v>1.167</v>
       </c>
       <c r="V30" t="n">
+        <v>1</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1</v>
+      </c>
+      <c r="X30" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1.167</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>0.583</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="AG30" t="n">
         <v>0.4</v>
       </c>
-      <c r="W30" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="X30" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AA30" t="n">
+      <c r="AH30" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>1.333</v>
+      </c>
+      <c r="AJ30" t="n">
         <v>0.375</v>
       </c>
-      <c r="AB30" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="AD30" t="n">
+      <c r="AK30" t="n">
         <v>0.5</v>
       </c>
-      <c r="AE30" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="AG30" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AH30" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AI30" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AJ30" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="AK30" t="n">
-        <v>0.6</v>
-      </c>
       <c r="AL30" t="n">
-        <v>1.8</v>
+        <v>1.833</v>
       </c>
       <c r="AM30" t="n">
-        <v>0.333</v>
+        <v>0.273</v>
       </c>
       <c r="AN30" t="inlineStr">
         <is>
-          <t>22:06</t>
+          <t>23:05</t>
         </is>
       </c>
       <c r="AO30" t="n">
-        <v>7.528</v>
+        <v>8.587</v>
       </c>
       <c r="AP30" t="n">
-        <v>0.468</v>
+        <v>0.476</v>
       </c>
       <c r="AQ30" t="n">
-        <v>0.476</v>
+        <v>0.494</v>
       </c>
       <c r="AR30" t="n">
-        <v>0.85</v>
+        <v>0.873</v>
       </c>
       <c r="AS30" t="n">
-        <v>0.106</v>
+        <v>0.116</v>
       </c>
       <c r="AT30" t="n">
-        <v>0.097</v>
+        <v>0.119</v>
       </c>
       <c r="AU30" t="n">
-        <v>1</v>
+        <v>1.167</v>
       </c>
       <c r="AV30" t="n">
-        <v>7.75</v>
+        <v>7</v>
       </c>
       <c r="AW30" t="n">
-        <v>8.75</v>
+        <v>8.167</v>
       </c>
       <c r="AX30" t="n">
-        <v>0.156</v>
+        <v>0.169</v>
       </c>
       <c r="AY30" t="n">
-        <v>0.083</v>
+        <v>0.102</v>
       </c>
       <c r="AZ30" t="n">
-        <v>0.18</v>
+        <v>0.184</v>
       </c>
       <c r="BA30" t="n">
-        <v>0.028</v>
+        <v>0.042</v>
       </c>
     </row>
     <row r="31">
@@ -5118,16 +5118,16 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C31" t="n">
-        <v>9.800000000000001</v>
+        <v>9.167</v>
       </c>
       <c r="D31" t="n">
-        <v>3.8</v>
+        <v>3.667</v>
       </c>
       <c r="E31" t="n">
-        <v>7.4</v>
+        <v>7.333</v>
       </c>
       <c r="F31" t="n">
         <v>0</v>
@@ -5136,82 +5136,82 @@
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>2.2</v>
+        <v>1.833</v>
       </c>
       <c r="I31" t="n">
-        <v>3.2</v>
+        <v>2.667</v>
       </c>
       <c r="J31" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="K31" t="n">
-        <v>3</v>
+        <v>3.333</v>
       </c>
       <c r="L31" t="n">
-        <v>2.6</v>
+        <v>2.833</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>0.167</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>0.167</v>
       </c>
       <c r="O31" t="n">
         <v>2</v>
       </c>
       <c r="P31" t="n">
-        <v>0.8</v>
+        <v>1.167</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.4</v>
+        <v>0.833</v>
       </c>
       <c r="R31" t="n">
-        <v>3.4</v>
+        <v>3.667</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="U31" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="V31" t="n">
-        <v>1.6</v>
+        <v>1.333</v>
       </c>
       <c r="W31" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="X31" t="n">
-        <v>1.2</v>
+        <v>1.333</v>
       </c>
       <c r="Y31" t="n">
-        <v>2.8</v>
+        <v>2.667</v>
       </c>
       <c r="Z31" t="n">
-        <v>4.4</v>
+        <v>4.333</v>
       </c>
       <c r="AA31" t="n">
-        <v>0.636</v>
+        <v>0.615</v>
       </c>
       <c r="AB31" t="n">
-        <v>1</v>
+        <v>0.833</v>
       </c>
       <c r="AC31" t="n">
-        <v>2.8</v>
+        <v>2.667</v>
       </c>
       <c r="AD31" t="n">
-        <v>0.357</v>
+        <v>0.313</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>0.167</v>
       </c>
       <c r="AF31" t="n">
-        <v>0.2</v>
+        <v>0.333</v>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AH31" t="n">
         <v>0</v>
@@ -5233,47 +5233,47 @@
       </c>
       <c r="AN31" t="inlineStr">
         <is>
-          <t>22:05</t>
+          <t>21:29</t>
         </is>
       </c>
       <c r="AO31" t="n">
-        <v>9.608000000000001</v>
+        <v>9.673</v>
       </c>
       <c r="AP31" t="n">
-        <v>0.514</v>
+        <v>0.5</v>
       </c>
       <c r="AQ31" t="n">
-        <v>0.556</v>
+        <v>0.539</v>
       </c>
       <c r="AR31" t="n">
-        <v>1.02</v>
+        <v>0.948</v>
       </c>
       <c r="AS31" t="n">
-        <v>0.083</v>
+        <v>0.121</v>
       </c>
       <c r="AT31" t="n">
-        <v>0.297</v>
+        <v>0.25</v>
       </c>
       <c r="AU31" t="n">
-        <v>0.75</v>
+        <v>0.429</v>
       </c>
       <c r="AV31" t="n">
-        <v>9.25</v>
+        <v>6.286</v>
       </c>
       <c r="AW31" t="n">
-        <v>10</v>
+        <v>6.714</v>
       </c>
       <c r="AX31" t="n">
-        <v>0.199</v>
+        <v>0.204</v>
       </c>
       <c r="AY31" t="n">
-        <v>0.12</v>
+        <v>0.133</v>
       </c>
       <c r="AZ31" t="n">
-        <v>0.135</v>
+        <v>0.158</v>
       </c>
       <c r="BA31" t="n">
-        <v>0.022</v>
+        <v>0.019</v>
       </c>
     </row>
     <row r="32">
@@ -5283,88 +5283,88 @@
         </is>
       </c>
       <c r="B32" t="n">
+        <v>6</v>
+      </c>
+      <c r="C32" t="n">
+        <v>2.667</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="E32" t="n">
+        <v>1.833</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="G32" t="n">
+        <v>3</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="K32" t="n">
+        <v>1.833</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="S32" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
         <v>5</v>
       </c>
-      <c r="C32" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="D32" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="E32" t="n">
-        <v>2</v>
-      </c>
-      <c r="F32" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="G32" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="H32" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="I32" t="n">
-        <v>1</v>
-      </c>
-      <c r="J32" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="K32" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="L32" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="M32" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="N32" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="O32" t="n">
-        <v>0</v>
-      </c>
-      <c r="P32" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="R32" t="n">
-        <v>1</v>
-      </c>
-      <c r="S32" t="n">
-        <v>0</v>
-      </c>
-      <c r="T32" t="n">
-        <v>7</v>
-      </c>
       <c r="U32" t="n">
-        <v>0.4</v>
+        <v>0.333</v>
       </c>
       <c r="V32" t="n">
-        <v>0.4</v>
+        <v>0.333</v>
       </c>
       <c r="W32" t="n">
-        <v>0.4</v>
+        <v>0.333</v>
       </c>
       <c r="X32" t="n">
-        <v>0.2</v>
+        <v>0.167</v>
       </c>
       <c r="Y32" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.4</v>
+        <v>1.333</v>
       </c>
       <c r="AA32" t="n">
-        <v>0.429</v>
+        <v>0.375</v>
       </c>
       <c r="AB32" t="n">
-        <v>0.2</v>
+        <v>0.167</v>
       </c>
       <c r="AC32" t="n">
-        <v>0.2</v>
+        <v>0.167</v>
       </c>
       <c r="AD32" t="n">
         <v>1</v>
@@ -5373,72 +5373,72 @@
         <v>0</v>
       </c>
       <c r="AF32" t="n">
-        <v>0.4</v>
+        <v>0.333</v>
       </c>
       <c r="AG32" t="n">
         <v>0</v>
       </c>
       <c r="AH32" t="n">
-        <v>0.2</v>
+        <v>0.167</v>
       </c>
       <c r="AI32" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="AJ32" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.067</v>
       </c>
       <c r="AK32" t="n">
-        <v>0.2</v>
+        <v>0.167</v>
       </c>
       <c r="AL32" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="AM32" t="n">
         <v>0.333</v>
       </c>
       <c r="AN32" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AO32" t="n">
-        <v>6.44</v>
+        <v>5.7</v>
       </c>
       <c r="AP32" t="n">
-        <v>0.259</v>
+        <v>0.241</v>
       </c>
       <c r="AQ32" t="n">
-        <v>0.274</v>
+        <v>0.256</v>
       </c>
       <c r="AR32" t="n">
-        <v>0.497</v>
+        <v>0.468</v>
       </c>
       <c r="AS32" t="n">
-        <v>0.093</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="AT32" t="n">
-        <v>0.074</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="AU32" t="n">
         <v>0.667</v>
       </c>
       <c r="AV32" t="n">
-        <v>9</v>
+        <v>9.667</v>
       </c>
       <c r="AW32" t="n">
-        <v>9.667</v>
+        <v>10.333</v>
       </c>
       <c r="AX32" t="n">
-        <v>0.192</v>
+        <v>0.186</v>
       </c>
       <c r="AY32" t="n">
-        <v>0.053</v>
+        <v>0.048</v>
       </c>
       <c r="AZ32" t="n">
-        <v>0.143</v>
+        <v>0.135</v>
       </c>
       <c r="BA32" t="n">
-        <v>0.013</v>
+        <v>0.011</v>
       </c>
     </row>
     <row r="33">
@@ -5448,16 +5448,16 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C33" t="n">
         <v>8</v>
       </c>
       <c r="D33" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="E33" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
@@ -5466,49 +5466,49 @@
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="I33" t="n">
-        <v>1.4</v>
+        <v>1.167</v>
       </c>
       <c r="J33" t="n">
-        <v>0.4</v>
+        <v>0.333</v>
       </c>
       <c r="K33" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L33" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="M33" t="n">
-        <v>0.2</v>
+        <v>0.167</v>
       </c>
       <c r="N33" t="n">
-        <v>0.4</v>
+        <v>0.333</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>0.4</v>
+        <v>0.833</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>0.333</v>
       </c>
       <c r="R33" t="n">
-        <v>1.4</v>
+        <v>1.333</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="U33" t="n">
-        <v>0.8</v>
+        <v>0.667</v>
       </c>
       <c r="V33" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="W33" t="n">
         <v>0</v>
@@ -5517,28 +5517,28 @@
         <v>0</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.8</v>
+        <v>1.833</v>
       </c>
       <c r="Z33" t="n">
-        <v>3.2</v>
+        <v>3.333</v>
       </c>
       <c r="AA33" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.55</v>
       </c>
       <c r="AB33" t="n">
+        <v>1.167</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1.667</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AF33" t="n">
         <v>1</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>0.714</v>
-      </c>
-      <c r="AE33" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>1.2</v>
       </c>
       <c r="AG33" t="n">
         <v>0.5</v>
@@ -5563,47 +5563,47 @@
       </c>
       <c r="AN33" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AO33" t="n">
-        <v>6.816</v>
+        <v>7.347</v>
       </c>
       <c r="AP33" t="n">
-        <v>0.586</v>
+        <v>0.583</v>
       </c>
       <c r="AQ33" t="n">
-        <v>0.623</v>
+        <v>0.614</v>
       </c>
       <c r="AR33" t="n">
-        <v>1.174</v>
+        <v>1.089</v>
       </c>
       <c r="AS33" t="n">
-        <v>0.059</v>
+        <v>0.113</v>
       </c>
       <c r="AT33" t="n">
-        <v>0.207</v>
+        <v>0.167</v>
       </c>
       <c r="AU33" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="AV33" t="n">
-        <v>14.5</v>
+        <v>7.2</v>
       </c>
       <c r="AW33" t="n">
-        <v>15.5</v>
+        <v>7.6</v>
       </c>
       <c r="AX33" t="n">
-        <v>0.182</v>
+        <v>0.186</v>
       </c>
       <c r="AY33" t="n">
-        <v>0.154</v>
+        <v>0.141</v>
       </c>
       <c r="AZ33" t="n">
-        <v>0.266</v>
+        <v>0.256</v>
       </c>
       <c r="BA33" t="n">
-        <v>0.014</v>
+        <v>0.012</v>
       </c>
     </row>
     <row r="34">
@@ -5613,40 +5613,40 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C34" t="n">
-        <v>8.199999999999999</v>
+        <v>6.833</v>
       </c>
       <c r="D34" t="n">
-        <v>2</v>
+        <v>1.667</v>
       </c>
       <c r="E34" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="F34" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="G34" t="n">
-        <v>1.8</v>
+        <v>1.833</v>
       </c>
       <c r="H34" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="I34" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J34" t="n">
-        <v>0.4</v>
+        <v>0.333</v>
       </c>
       <c r="K34" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="L34" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="M34" t="n">
-        <v>0.8</v>
+        <v>0.667</v>
       </c>
       <c r="N34" t="n">
         <v>0</v>
@@ -5655,25 +5655,25 @@
         <v>1</v>
       </c>
       <c r="P34" t="n">
-        <v>0.2</v>
+        <v>0.167</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>1.8</v>
+        <v>1.833</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="U34" t="n">
         <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>0.8</v>
+        <v>0.667</v>
       </c>
       <c r="W34" t="n">
         <v>0</v>
@@ -5682,28 +5682,28 @@
         <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.4</v>
+        <v>1.167</v>
       </c>
       <c r="Z34" t="n">
-        <v>2</v>
+        <v>1.833</v>
       </c>
       <c r="AA34" t="n">
-        <v>0.7</v>
+        <v>0.636</v>
       </c>
       <c r="AB34" t="n">
-        <v>0.4</v>
+        <v>0.333</v>
       </c>
       <c r="AC34" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="AD34" t="n">
         <v>0.667</v>
       </c>
       <c r="AE34" t="n">
-        <v>0.2</v>
+        <v>0.167</v>
       </c>
       <c r="AF34" t="n">
-        <v>0.8</v>
+        <v>0.667</v>
       </c>
       <c r="AG34" t="n">
         <v>0.25</v>
@@ -5712,63 +5712,63 @@
         <v>0</v>
       </c>
       <c r="AI34" t="n">
-        <v>0.2</v>
+        <v>0.333</v>
       </c>
       <c r="AJ34" t="n">
         <v>0</v>
       </c>
       <c r="AK34" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="AL34" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AM34" t="n">
-        <v>0.75</v>
+        <v>0.667</v>
       </c>
       <c r="AN34" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="AO34" t="n">
-        <v>5.928</v>
+        <v>5.44</v>
       </c>
       <c r="AP34" t="n">
-        <v>0.731</v>
+        <v>0.655</v>
       </c>
       <c r="AQ34" t="n">
-        <v>0.716</v>
+        <v>0.648</v>
       </c>
       <c r="AR34" t="n">
-        <v>1.383</v>
+        <v>1.256</v>
       </c>
       <c r="AS34" t="n">
-        <v>0.034</v>
+        <v>0.031</v>
       </c>
       <c r="AT34" t="n">
-        <v>0.115</v>
+        <v>0.103</v>
       </c>
       <c r="AU34" t="n">
         <v>2</v>
       </c>
       <c r="AV34" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="AW34" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="AX34" t="n">
-        <v>0.153</v>
+        <v>0.148</v>
       </c>
       <c r="AY34" t="n">
-        <v>0.06900000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="AZ34" t="n">
-        <v>0.168</v>
+        <v>0.152</v>
       </c>
       <c r="BA34" t="n">
-        <v>0.014</v>
+        <v>0.012</v>
       </c>
     </row>
     <row r="35">
@@ -5778,7 +5778,7 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C35" t="n">
         <v>0</v>
@@ -5943,7 +5943,7 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C36" t="n">
         <v>0</v>
@@ -5970,7 +5970,7 @@
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>1.6</v>
+        <v>2.167</v>
       </c>
       <c r="L36" t="n">
         <v>2</v>
@@ -5985,10 +5985,10 @@
         <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>0.8</v>
+        <v>0.667</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.8</v>
+        <v>0.667</v>
       </c>
       <c r="R36" t="n">
         <v>0</v>
@@ -6108,118 +6108,118 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C37" t="n">
-        <v>84.40000000000001</v>
+        <v>82.167</v>
       </c>
       <c r="D37" t="n">
-        <v>19.2</v>
+        <v>19.667</v>
       </c>
       <c r="E37" t="n">
-        <v>40.4</v>
+        <v>40.5</v>
       </c>
       <c r="F37" t="n">
-        <v>11.8</v>
+        <v>10.833</v>
       </c>
       <c r="G37" t="n">
-        <v>29.4</v>
+        <v>29</v>
       </c>
       <c r="H37" t="n">
-        <v>10.6</v>
+        <v>10.333</v>
       </c>
       <c r="I37" t="n">
-        <v>16</v>
+        <v>15.333</v>
       </c>
       <c r="J37" t="n">
-        <v>15.8</v>
+        <v>15.833</v>
       </c>
       <c r="K37" t="n">
-        <v>28.2</v>
+        <v>27.833</v>
       </c>
       <c r="L37" t="n">
-        <v>14.4</v>
+        <v>14.667</v>
       </c>
       <c r="M37" t="n">
-        <v>5.8</v>
+        <v>6.667</v>
       </c>
       <c r="N37" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="O37" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="P37" t="n">
-        <v>10.4</v>
+        <v>11.833</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.2</v>
+        <v>4.5</v>
       </c>
       <c r="R37" t="n">
-        <v>20.8</v>
+        <v>21.167</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>354</v>
+        <v>401</v>
       </c>
       <c r="U37" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="V37" t="n">
-        <v>8.6</v>
+        <v>8.833</v>
       </c>
       <c r="W37" t="n">
-        <v>8.800000000000001</v>
+        <v>10.833</v>
       </c>
       <c r="X37" t="n">
-        <v>4</v>
+        <v>4.833</v>
       </c>
       <c r="Y37" t="n">
-        <v>10.8</v>
+        <v>11.333</v>
       </c>
       <c r="Z37" t="n">
-        <v>20.8</v>
+        <v>21.333</v>
       </c>
       <c r="AA37" t="n">
-        <v>0.519</v>
+        <v>0.531</v>
       </c>
       <c r="AB37" t="n">
-        <v>6</v>
+        <v>6.167</v>
       </c>
       <c r="AC37" t="n">
-        <v>12.8</v>
+        <v>13</v>
       </c>
       <c r="AD37" t="n">
-        <v>0.469</v>
+        <v>0.474</v>
       </c>
       <c r="AE37" t="n">
-        <v>2.4</v>
+        <v>2.167</v>
       </c>
       <c r="AF37" t="n">
-        <v>6.8</v>
+        <v>6.167</v>
       </c>
       <c r="AG37" t="n">
-        <v>0.353</v>
+        <v>0.351</v>
       </c>
       <c r="AH37" t="n">
-        <v>2.2</v>
+        <v>2.167</v>
       </c>
       <c r="AI37" t="n">
-        <v>8.800000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="AJ37" t="n">
-        <v>0.25</v>
+        <v>0.255</v>
       </c>
       <c r="AK37" t="n">
-        <v>9.6</v>
+        <v>8.667</v>
       </c>
       <c r="AL37" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="AM37" t="n">
-        <v>0.466</v>
+        <v>0.423</v>
       </c>
       <c r="AN37" t="inlineStr">
         <is>
@@ -6227,40 +6227,40 @@
         </is>
       </c>
       <c r="AO37" t="n">
-        <v>87.23999999999999</v>
+        <v>88.08</v>
       </c>
       <c r="AP37" t="n">
-        <v>0.529</v>
+        <v>0.517</v>
       </c>
       <c r="AQ37" t="n">
-        <v>0.549</v>
+        <v>0.539</v>
       </c>
       <c r="AR37" t="n">
-        <v>0.967</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="AS37" t="n">
-        <v>0.119</v>
+        <v>0.134</v>
       </c>
       <c r="AT37" t="n">
-        <v>0.152</v>
+        <v>0.149</v>
       </c>
       <c r="AU37" t="n">
-        <v>1.519</v>
+        <v>1.338</v>
       </c>
       <c r="AV37" t="n">
-        <v>6.712</v>
+        <v>5.873</v>
       </c>
       <c r="AW37" t="n">
-        <v>8.231</v>
+        <v>7.211</v>
       </c>
       <c r="AX37" t="n">
         <v>0.2</v>
       </c>
       <c r="AY37" t="n">
-        <v>0.073</v>
+        <v>0.074</v>
       </c>
       <c r="AZ37" t="n">
-        <v>0.14</v>
+        <v>0.142</v>
       </c>
       <c r="BA37" t="n">
         <v>0</v>
@@ -6273,118 +6273,118 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C38" t="n">
-        <v>71.8</v>
+        <v>69.167</v>
       </c>
       <c r="D38" t="n">
-        <v>16.6</v>
+        <v>16.167</v>
       </c>
       <c r="E38" t="n">
-        <v>37</v>
+        <v>35.833</v>
       </c>
       <c r="F38" t="n">
-        <v>7.6</v>
+        <v>7.167</v>
       </c>
       <c r="G38" t="n">
-        <v>25.4</v>
+        <v>25.167</v>
       </c>
       <c r="H38" t="n">
-        <v>15.8</v>
+        <v>15.333</v>
       </c>
       <c r="I38" t="n">
-        <v>19.8</v>
+        <v>20</v>
       </c>
       <c r="J38" t="n">
-        <v>11.8</v>
+        <v>11.167</v>
       </c>
       <c r="K38" t="n">
-        <v>24.8</v>
+        <v>25</v>
       </c>
       <c r="L38" t="n">
-        <v>12</v>
+        <v>11.333</v>
       </c>
       <c r="M38" t="n">
-        <v>7.2</v>
+        <v>7.333</v>
       </c>
       <c r="N38" t="n">
-        <v>1.2</v>
+        <v>1.167</v>
       </c>
       <c r="O38" t="n">
         <v>8</v>
       </c>
       <c r="P38" t="n">
-        <v>12</v>
+        <v>13.167</v>
       </c>
       <c r="Q38" t="n">
-        <v>6.2</v>
+        <v>6.5</v>
       </c>
       <c r="R38" t="n">
-        <v>20.4</v>
+        <v>20.167</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>245</v>
+        <v>269</v>
       </c>
       <c r="U38" t="n">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="V38" t="n">
-        <v>7.4</v>
+        <v>6.667</v>
       </c>
       <c r="W38" t="n">
-        <v>12.4</v>
+        <v>12.333</v>
       </c>
       <c r="X38" t="n">
-        <v>6.6</v>
+        <v>6.333</v>
       </c>
       <c r="Y38" t="n">
-        <v>11</v>
+        <v>10.667</v>
       </c>
       <c r="Z38" t="n">
-        <v>18.8</v>
+        <v>17.833</v>
       </c>
       <c r="AA38" t="n">
-        <v>0.585</v>
+        <v>0.598</v>
       </c>
       <c r="AB38" t="n">
-        <v>3.4</v>
+        <v>3.333</v>
       </c>
       <c r="AC38" t="n">
-        <v>12.2</v>
+        <v>11.833</v>
       </c>
       <c r="AD38" t="n">
-        <v>0.279</v>
+        <v>0.282</v>
       </c>
       <c r="AE38" t="n">
-        <v>2.2</v>
+        <v>2.167</v>
       </c>
       <c r="AF38" t="n">
-        <v>6</v>
+        <v>6.167</v>
       </c>
       <c r="AG38" t="n">
-        <v>0.367</v>
+        <v>0.351</v>
       </c>
       <c r="AH38" t="n">
-        <v>1</v>
+        <v>0.833</v>
       </c>
       <c r="AI38" t="n">
-        <v>5.8</v>
+        <v>5.167</v>
       </c>
       <c r="AJ38" t="n">
-        <v>0.172</v>
+        <v>0.161</v>
       </c>
       <c r="AK38" t="n">
-        <v>6.6</v>
+        <v>6.333</v>
       </c>
       <c r="AL38" t="n">
-        <v>19.6</v>
+        <v>20</v>
       </c>
       <c r="AM38" t="n">
-        <v>0.337</v>
+        <v>0.317</v>
       </c>
       <c r="AN38" t="inlineStr">
         <is>
@@ -6392,40 +6392,40 @@
         </is>
       </c>
       <c r="AO38" t="n">
-        <v>83.11199999999999</v>
+        <v>82.967</v>
       </c>
       <c r="AP38" t="n">
-        <v>0.449</v>
+        <v>0.441</v>
       </c>
       <c r="AQ38" t="n">
-        <v>0.505</v>
+        <v>0.495</v>
       </c>
       <c r="AR38" t="n">
-        <v>0.864</v>
+        <v>0.834</v>
       </c>
       <c r="AS38" t="n">
-        <v>0.144</v>
+        <v>0.159</v>
       </c>
       <c r="AT38" t="n">
-        <v>0.253</v>
+        <v>0.251</v>
       </c>
       <c r="AU38" t="n">
-        <v>0.983</v>
+        <v>0.848</v>
       </c>
       <c r="AV38" t="n">
-        <v>5.2</v>
+        <v>4.633</v>
       </c>
       <c r="AW38" t="n">
-        <v>6.183</v>
+        <v>5.481</v>
       </c>
       <c r="AX38" t="n">
-        <v>0.191</v>
+        <v>0.188</v>
       </c>
       <c r="AY38" t="n">
-        <v>0.061</v>
+        <v>0.057</v>
       </c>
       <c r="AZ38" t="n">
-        <v>0.123</v>
+        <v>0.128</v>
       </c>
       <c r="BA38" t="n">
         <v>0</v>
